--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N70_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>10.73258632436499</v>
       </c>
       <c r="E2" t="n">
-        <v>2.224296706675025</v>
+        <v>2.42134026214377</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02201679413240676</v>
+        <v>2.449613037734396</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,55 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>5.324689945301454</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.514295486439195</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.42134026214377</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.449613037734396</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T6165</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0035F0001T0006Z000C1N70.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>6.497526070129637</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>10.68855273610018</v>
       </c>
-      <c r="E3" t="n">
-        <v>2.224296706675025</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.02201679413240676</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>2.42134026214377</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.449613037734396</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T6165</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>10.94611948347969</v>
+        <v>1.778744416065449</v>
       </c>
       <c r="D2" t="n">
-        <v>10.73258632436499</v>
+        <v>1.744045277709311</v>
       </c>
       <c r="E2" t="n">
-        <v>2.42134026214377</v>
+        <v>0.3934677925983627</v>
       </c>
       <c r="F2" t="n">
-        <v>2.449613037734396</v>
+        <v>0.3980621186318393</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.324689945301454</v>
+        <v>0.8652621161114863</v>
       </c>
       <c r="D3" t="n">
-        <v>5.514295486439195</v>
+        <v>0.8960730165463693</v>
       </c>
       <c r="E3" t="n">
-        <v>2.42134026214377</v>
+        <v>0.3934677925983627</v>
       </c>
       <c r="F3" t="n">
-        <v>2.449613037734396</v>
+        <v>0.3980621186318393</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.497526070129637</v>
+        <v>1.055847986396066</v>
       </c>
       <c r="D4" t="n">
-        <v>10.68855273610018</v>
+        <v>1.736889819616279</v>
       </c>
       <c r="E4" t="n">
-        <v>2.42134026214377</v>
+        <v>0.3934677925983627</v>
       </c>
       <c r="F4" t="n">
-        <v>2.449613037734396</v>
+        <v>0.3980621186318393</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
